--- a/ID804/ID804_FA_Board/Docs/Firmware_Development_Documentation.xlsx
+++ b/ID804/ID804_FA_Board/Docs/Firmware_Development_Documentation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\ID804\ID804_TEST\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\ID804\ID804_FA_Board\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92BFA73-4AD0-46AD-9778-314F3E12BBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB09F51-3CD1-41B1-8007-FF6E43E20F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Summary" sheetId="14" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="272">
   <si>
     <t>Requirement ID</t>
   </si>
@@ -941,6 +941,14 @@
   </si>
   <si>
     <t>STM32 LL / UART / FLASH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FW-REQ-008</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The The firmware shall not use HAL_Delay or LL_mDelay.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2049,7 +2057,28 @@
       </c>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="10" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="4"/>
+    </row>
     <row r="11" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="12" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="13" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -2067,19 +2096,19 @@
           <x14:formula1>
             <xm:f>Common!$D$3:$D$7</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H9</xm:sqref>
+          <xm:sqref>H3:H10</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5DF9B7D1-31DB-4402-87DE-866074A4475D}">
           <x14:formula1>
             <xm:f>Common!$B$3:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>E3:E9</xm:sqref>
+          <xm:sqref>E3:E10</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A450BA07-13EB-4D36-880F-44F80B40A943}">
           <x14:formula1>
             <xm:f>Common!$C$3:$C$4</xm:f>
           </x14:formula1>
-          <xm:sqref>F3:F9</xm:sqref>
+          <xm:sqref>F3:F10</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/ID804/ID804_FA_Board/Docs/Firmware_Development_Documentation.xlsx
+++ b/ID804/ID804_FA_Board/Docs/Firmware_Development_Documentation.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB09F51-3CD1-41B1-8007-FF6E43E20F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" tabRatio="875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Summary" sheetId="14" r:id="rId1"/>

--- a/ID804/ID804_FA_Board/Docs/Firmware_Development_Documentation.xlsx
+++ b/ID804/ID804_FA_Board/Docs/Firmware_Development_Documentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\ID804\ID804_FA_Board\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB09F51-3CD1-41B1-8007-FF6E43E20F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8E7D56-6B30-489B-8FDF-F9FD51894CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" tabRatio="875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" tabRatio="875" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Summary" sheetId="14" r:id="rId1"/>
@@ -19,11 +19,12 @@
     <sheet name="03_Software Design" sheetId="3" r:id="rId4"/>
     <sheet name="04_Integrate Test" sheetId="4" r:id="rId5"/>
     <sheet name="05_System Test" sheetId="5" r:id="rId6"/>
-    <sheet name="MCU Setting" sheetId="11" r:id="rId7"/>
-    <sheet name="Static Analysis" sheetId="6" r:id="rId8"/>
-    <sheet name="Release Note" sheetId="7" r:id="rId9"/>
-    <sheet name="Traceability" sheetId="8" r:id="rId10"/>
-    <sheet name="Common" sheetId="9" r:id="rId11"/>
+    <sheet name="06_CLI" sheetId="15" r:id="rId7"/>
+    <sheet name="MCU Setting" sheetId="11" r:id="rId8"/>
+    <sheet name="Static Analysis" sheetId="6" r:id="rId9"/>
+    <sheet name="Release Note" sheetId="7" r:id="rId10"/>
+    <sheet name="Traceability" sheetId="8" r:id="rId11"/>
+    <sheet name="Common" sheetId="9" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00_Summary'!$B$2:$I$14</definedName>
@@ -32,9 +33,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_Software Design'!$B$2:$J$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_Integrate Test'!$B$2:$K$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_System Test'!$B$2:$L$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Release Note'!$B$2:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Static Analysis'!$B$2:$M$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Traceability!$B$2:$K$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Release Note'!$B$2:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Static Analysis'!$B$2:$M$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Traceability!$B$2:$K$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="365">
   <si>
     <t>Requirement ID</t>
   </si>
@@ -949,6 +950,327 @@
   </si>
   <si>
     <t>The The firmware shall not use HAL_Delay or LL_mDelay.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>명령어</t>
+  </si>
+  <si>
+    <t>매개변수 (Parameters)</t>
+  </si>
+  <si>
+    <t>설명 및 동작</t>
+  </si>
+  <si>
+    <t>사용 예시</t>
+  </si>
+  <si>
+    <t>비고 및 주의사항 (Notes)</t>
+  </si>
+  <si>
+    <t>help</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>도움말 정보 출력</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>reset</t>
+  </si>
+  <si>
+    <t>전체 시스템(메인 MCU) 리셋</t>
+  </si>
+  <si>
+    <t>id804_vdd</t>
+  </si>
+  <si>
+    <t>&lt;0: OFF, 1: 5V, 2: 5.5V&gt;</t>
+  </si>
+  <si>
+    <t>ID804 VDD 전압 제어</t>
+  </si>
+  <si>
+    <t>id804_vdd 1</t>
+  </si>
+  <si>
+    <t>id804_vled</t>
+  </si>
+  <si>
+    <t>ID804 VLED 전원 제어</t>
+  </si>
+  <si>
+    <t>id804_vled 1</t>
+  </si>
+  <si>
+    <t>id804_tm0</t>
+  </si>
+  <si>
+    <t>&lt;0: GND, 1: VDD&gt;</t>
+  </si>
+  <si>
+    <t>ID804 TM0 핀 논리 수준 제어</t>
+  </si>
+  <si>
+    <t>id804_tm0 0</t>
+  </si>
+  <si>
+    <t>id804_sio1</t>
+  </si>
+  <si>
+    <t>SIO1 인터페이스 통신 경로 선택 및 활성화</t>
+  </si>
+  <si>
+    <t>id804_sio2</t>
+  </si>
+  <si>
+    <t>SIO2 인터페이스 통신 경로 선택 및 활성화</t>
+  </si>
+  <si>
+    <t>id804_boot_single</t>
+  </si>
+  <si>
+    <t>&lt;0: MCU, 1: I2C&gt;</t>
+  </si>
+  <si>
+    <t>ID804 Single 부팅 시 통신 방식 설정</t>
+  </si>
+  <si>
+    <t>id804_boot_forward</t>
+  </si>
+  <si>
+    <t>&lt;0: LVDS, 1: CAN&gt;</t>
+  </si>
+  <si>
+    <t>ID804 Forward 부팅 시 통신 방식 설정</t>
+  </si>
+  <si>
+    <t>id804_boot_backward</t>
+  </si>
+  <si>
+    <t>ID804 Backward 부팅 시 통신 방식 설정</t>
+  </si>
+  <si>
+    <t>id804_reset</t>
+  </si>
+  <si>
+    <t>&lt;Dev Addr&gt;</t>
+  </si>
+  <si>
+    <t>id804_initbidir</t>
+  </si>
+  <si>
+    <t>id804_clrerror</t>
+  </si>
+  <si>
+    <t>id804_gosleep</t>
+  </si>
+  <si>
+    <t>id804_goactive</t>
+  </si>
+  <si>
+    <t>id804_godeepsleep</t>
+  </si>
+  <si>
+    <t>id804_me</t>
+  </si>
+  <si>
+    <t>Read 시 Data 인자는 생략</t>
+  </si>
+  <si>
+    <t>id804_i2c</t>
+  </si>
+  <si>
+    <t>I2C 인터페이스 레지스터 Read/Write</t>
+  </si>
+  <si>
+    <t>&lt;0: OFF, 1: 5V&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>id804_sio1 2 1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>id804_sio2 3 1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">id804_boot_single 0 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">id804_boot_forward 1 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">id804_boot_backward 0 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">id804_reset 0 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">id804_gosleep 10 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">id804_goactive 100 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">id804_godeepsleep 1000 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VDD 5V</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TM0 GND</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RESET, Broadcast</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>INITBIDIR, Dev Addr = 1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLRERROR, Broadcast</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GOSLEEP, Dev Addr = 10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GOACTIVE, Dev Addr = 100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>READ_RGB, Broadcast</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Address = 0x50, Data = 0xAB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Address = 0x50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SIO1 CAN 선택 후 Enable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>단일 제어, MCU 부팅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>복수 정방향 제어, CAN 부팅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>복수 역방향 제어, LVDS 부팅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지정 Dev Addr ID804 RESET</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지정 Dev Addr ID804 INITBIDIR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지정 Dev Addr ID804 CLRERROR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지정 Dev Addr ID804 GOSLEEP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지정 Dev Addr ID804 GOACTIVE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지정 Dev Addr ID804 GODEEPSLEEP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>M.E. 인터페이스 레지스터 Read/Write</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SIO2 LVDS 선택 후 Enable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>※ Boot 모드 변경 필요 시 보드 리셋 필요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>VLED 5V</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SET_RGB, Broadcast</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;인터페이스&gt; &lt;활성화&gt;</t>
+  </si>
+  <si>
+    <t>• 인터페이스: 1: MCU, 2: CAN, 3: LVDS, 4: I2C</t>
+  </si>
+  <si>
+    <t>• 활성화: 1: ENABLE, 0: DISABLE</t>
+  </si>
+  <si>
+    <t>• 인터페이스: 1: MCU, 2: CAN, 3: LVDS, 4: EOL</t>
+  </si>
+  <si>
+    <t>&lt;0: WRITE, 1: READ&gt; &lt;Dev Addr&gt; &lt;CMD&gt; &lt;Data&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• 쓰기: id804_me 0 0 0xA0 0xFFFFFF </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">• 읽기: id804_me 1 2 0x60 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;0: WRITE, 1: READ&gt; &lt;Address&gt; &lt;Data&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• 쓰기: id804_i2c 0 0x50 0xAB </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">• 읽기: id804_i2c 1 0x50 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>id804_initbidir 1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>id804_clrerror 0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GODEEPSLEEP, Dev Addr = 1000</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -961,7 +1283,7 @@
     <numFmt numFmtId="177" formatCode="0&quot;MHz&quot;"/>
     <numFmt numFmtId="178" formatCode="0.00&quot;MHz&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -996,6 +1318,31 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -1052,7 +1399,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1091,6 +1438,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1100,6 +1463,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF9933"/>
       <color rgb="FFFF3399"/>
       <color rgb="FFCC00FF"/>
       <color rgb="FF6666FF"/>
@@ -1595,6 +1959,147 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="B2:C18"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.58203125" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B3" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B5" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B6" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B7" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B8" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B9" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B10" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B11" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B12" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B13" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B14" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B17" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:C18" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B2:K7"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -1786,7 +2291,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4EECE6E-04CB-4201-95F0-D342C469E1BD}">
   <dimension ref="B2:D7"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -1868,7 +2373,7 @@
   <cols>
     <col min="1" max="1" width="2.58203125" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="86.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="91" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="21" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
@@ -2944,6 +3449,482 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F23DDBF-7655-41D3-8E35-D934A2646BBA}">
+  <sheetPr>
+    <tabColor rgb="FFFF9933"/>
+  </sheetPr>
+  <dimension ref="B1:G29"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.58203125" style="14" customWidth="1"/>
+    <col min="2" max="2" width="17.58203125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="41.58203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.83203125" style="14" customWidth="1"/>
+    <col min="5" max="5" width="28" style="14" customWidth="1"/>
+    <col min="6" max="6" width="69" style="14" customWidth="1"/>
+    <col min="7" max="7" width="38.83203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.6640625" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="F2" s="19"/>
+      <c r="G2" s="15" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+    </row>
+    <row r="4" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+    </row>
+    <row r="6" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="G6" s="16"/>
+    </row>
+    <row r="7" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="G7" s="16"/>
+    </row>
+    <row r="8" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="G8" s="16"/>
+    </row>
+    <row r="9" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>337</v>
+      </c>
+      <c r="G9" s="17"/>
+    </row>
+    <row r="10" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="17"/>
+      <c r="C10" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="17"/>
+    </row>
+    <row r="11" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="17"/>
+      <c r="C11" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="17"/>
+    </row>
+    <row r="12" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>348</v>
+      </c>
+      <c r="G12" s="17"/>
+    </row>
+    <row r="13" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="17"/>
+      <c r="C13" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="17"/>
+    </row>
+    <row r="14" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="17"/>
+      <c r="C14" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="17"/>
+    </row>
+    <row r="15" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>339</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="G18" s="16"/>
+    </row>
+    <row r="19" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="G19" s="16"/>
+    </row>
+    <row r="20" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B20" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="G20" s="16"/>
+    </row>
+    <row r="21" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B21" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="G21" s="16"/>
+    </row>
+    <row r="22" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="G22" s="16"/>
+    </row>
+    <row r="23" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>346</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="G23" s="16"/>
+    </row>
+    <row r="24" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B24" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="G25" s="17"/>
+    </row>
+    <row r="26" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="G27" s="17"/>
+    </row>
+    <row r="28" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="29" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45"/>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="F12:F14"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D9FE29F-E938-437A-A1E2-83FAA50DF5A9}">
   <dimension ref="B2:R19"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -3584,7 +4565,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:M4"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -3711,145 +4692,4 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B2:C18"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="2.58203125" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B3" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B4" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B5" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B6" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B7" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B8" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B9" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B10" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B11" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B12" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B13" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B14" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B17" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B18" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="B2:C18" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/ID804/ID804_FA_Board/Docs/Firmware_Development_Documentation.xlsx
+++ b/ID804/ID804_FA_Board/Docs/Firmware_Development_Documentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\ID804\ID804_FA_Board\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{911664C5-3379-46CF-A4A9-B62F505C2917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4CFC43B-9B2D-4C83-8FFE-7C0A841320E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" tabRatio="875" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" tabRatio="875" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Summary" sheetId="14" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="430">
   <si>
     <t>Requirement ID</t>
   </si>
@@ -252,9 +252,6 @@
   </si>
   <si>
     <t>Release Date</t>
-  </si>
-  <si>
-    <t>Release Type</t>
   </si>
   <si>
     <t>Binary</t>
@@ -1429,34 +1426,21 @@
     <t>ID804 FA Board</t>
   </si>
   <si>
-    <t>ID804_FA_Board_v0.2.43.bin</t>
-  </si>
-  <si>
-    <t>v0.2.43</t>
-  </si>
-  <si>
     <t>Summary</t>
   </si>
   <si>
-    <t>4df3782</t>
-  </si>
-  <si>
-    <t>Release</t>
-  </si>
-  <si>
     <t>Initial release</t>
   </si>
   <si>
-    <t>v0.2.44</t>
-  </si>
-  <si>
-    <t>a1b2c3d</t>
-  </si>
-  <si>
-    <t>ID804_FA_Board_v0.2.44.bin</t>
-  </si>
-  <si>
-    <t>Fixed I2C timeout handling</t>
+    <t>v0.3.0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>857be5d</t>
+  </si>
+  <si>
+    <t>ID804_FA_Board_v0.3.0_857be5d.bin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2088,10 +2072,10 @@
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B2" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -2099,7 +2083,7 @@
         <v>59</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -2107,7 +2091,7 @@
         <v>60</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -2115,45 +2099,45 @@
         <v>28</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B6" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>225</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B7" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="C7" s="21" t="s">
         <v>227</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B8" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="C8" s="20" t="s">
         <v>229</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B9" s="21" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C9" s="22"/>
     </row>
     <row r="10" spans="2:3" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B10" s="20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -2181,7 +2165,7 @@
   <sheetData>
     <row r="2" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>4</v>
@@ -2192,10 +2176,10 @@
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B3" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>12</v>
@@ -2203,36 +2187,36 @@
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B4" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B5" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2290,13 +2274,13 @@
     </row>
     <row r="3" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>9</v>
@@ -2308,7 +2292,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I3" s="4"/>
     </row>
@@ -2317,10 +2301,10 @@
         <v>13</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>9</v>
@@ -2329,10 +2313,10 @@
         <v>14</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I4" s="5"/>
     </row>
@@ -2341,10 +2325,10 @@
         <v>16</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>9</v>
@@ -2353,10 +2337,10 @@
         <v>14</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I5" s="5"/>
     </row>
@@ -2365,10 +2349,10 @@
         <v>18</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>9</v>
@@ -2377,10 +2361,10 @@
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I6" s="5"/>
     </row>
@@ -2389,10 +2373,10 @@
         <v>20</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>9</v>
@@ -2401,46 +2385,46 @@
         <v>14</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>9</v>
@@ -2449,34 +2433,34 @@
         <v>10</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>9</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>244</v>
       </c>
       <c r="I10" s="4"/>
     </row>
@@ -2562,25 +2546,25 @@
     </row>
     <row r="3" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>255</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>256</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I3" s="5"/>
     </row>
@@ -2592,19 +2576,19 @@
         <v>28</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>260</v>
-      </c>
       <c r="H4" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I4" s="12"/>
     </row>
@@ -2616,19 +2600,19 @@
         <v>31</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>264</v>
-      </c>
       <c r="H5" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I5" s="12"/>
     </row>
@@ -2640,19 +2624,19 @@
         <v>31</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>268</v>
-      </c>
       <c r="H6" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I6" s="5"/>
     </row>
@@ -2664,139 +2648,139 @@
         <v>31</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>271</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I7" s="5"/>
     </row>
     <row r="8" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>275</v>
-      </c>
       <c r="H8" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I8" s="5"/>
     </row>
     <row r="9" spans="2:9" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>277</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>278</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I9" s="5"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B10" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>282</v>
-      </c>
       <c r="H10" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B11" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>125</v>
-      </c>
       <c r="H11" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I11" s="12"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B12" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>28</v>
       </c>
       <c r="D12" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="F12" s="12" t="s">
         <v>287</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>288</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>8</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I12" s="12"/>
     </row>
@@ -2878,28 +2862,28 @@
         <v>40</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>294</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>295</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
@@ -2907,28 +2891,28 @@
         <v>42</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>296</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>297</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>41</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>300</v>
-      </c>
       <c r="J4" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.45">
@@ -2936,28 +2920,28 @@
         <v>43</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>303</v>
-      </c>
       <c r="H5" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.45">
@@ -2965,202 +2949,202 @@
         <v>44</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>307</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>16</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B7" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="D7" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="F7" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="H7" s="12" t="s">
         <v>341</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>342</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>16</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="D8" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="E8" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="F8" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="G8" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>317</v>
-      </c>
       <c r="H8" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="D9" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="E9" s="12" t="s">
         <v>320</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>321</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>41</v>
       </c>
       <c r="G9" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="H9" s="12" t="s">
         <v>322</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>323</v>
       </c>
       <c r="I9" s="12" t="s">
         <v>20</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="D10" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="E10" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="F10" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="G10" s="12" t="s">
         <v>328</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="H10" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="H10" s="12" t="s">
-        <v>330</v>
-      </c>
       <c r="I10" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="F11" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="E11" s="12" t="s">
+      <c r="G11" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="H11" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="F11" s="12" t="s">
-        <v>332</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>346</v>
-      </c>
       <c r="I11" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D12" s="12" t="s">
+      <c r="E12" s="12" t="s">
         <v>335</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>336</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="H12" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="H12" s="12" t="s">
-        <v>338</v>
-      </c>
       <c r="I12" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -3231,220 +3215,220 @@
         <v>52</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>351</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B4" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B5" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B6" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>366</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B7" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>370</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C8" t="s">
         <v>52</v>
       </c>
       <c r="D8" t="s">
+        <v>372</v>
+      </c>
+      <c r="E8" t="s">
         <v>373</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>374</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>386</v>
+      </c>
+      <c r="H8" t="s">
+        <v>232</v>
+      </c>
+      <c r="I8" t="s">
+        <v>349</v>
+      </c>
+      <c r="J8" t="s">
+        <v>274</v>
+      </c>
+      <c r="K8" t="s">
         <v>375</v>
-      </c>
-      <c r="G8" t="s">
-        <v>387</v>
-      </c>
-      <c r="H8" t="s">
-        <v>233</v>
-      </c>
-      <c r="I8" t="s">
-        <v>350</v>
-      </c>
-      <c r="J8" t="s">
-        <v>275</v>
-      </c>
-      <c r="K8" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C9" t="s">
         <v>52</v>
       </c>
       <c r="D9" t="s">
+        <v>377</v>
+      </c>
+      <c r="E9" t="s">
         <v>378</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>379</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>380</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
+        <v>232</v>
+      </c>
+      <c r="I9" t="s">
+        <v>349</v>
+      </c>
+      <c r="J9" t="s">
+        <v>274</v>
+      </c>
+      <c r="K9" t="s">
         <v>381</v>
-      </c>
-      <c r="H9" t="s">
-        <v>233</v>
-      </c>
-      <c r="I9" t="s">
-        <v>350</v>
-      </c>
-      <c r="J9" t="s">
-        <v>275</v>
-      </c>
-      <c r="K9" t="s">
-        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -3519,31 +3503,31 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.45">
@@ -3554,31 +3538,31 @@
         <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.45">
@@ -3589,31 +3573,31 @@
         <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
@@ -3624,31 +3608,31 @@
         <v>18</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.45">
@@ -3659,171 +3643,171 @@
         <v>20</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>406</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E8" t="s">
+        <v>407</v>
+      </c>
+      <c r="F8" t="s">
         <v>408</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>232</v>
+      </c>
+      <c r="H8" t="s">
+        <v>349</v>
+      </c>
+      <c r="I8" t="s">
+        <v>229</v>
+      </c>
+      <c r="J8" t="s">
+        <v>132</v>
+      </c>
+      <c r="K8" t="s">
+        <v>132</v>
+      </c>
+      <c r="L8" t="s">
         <v>409</v>
-      </c>
-      <c r="G8" t="s">
-        <v>233</v>
-      </c>
-      <c r="H8" t="s">
-        <v>350</v>
-      </c>
-      <c r="I8" t="s">
-        <v>230</v>
-      </c>
-      <c r="J8" t="s">
-        <v>133</v>
-      </c>
-      <c r="K8" t="s">
-        <v>133</v>
-      </c>
-      <c r="L8" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
+        <v>410</v>
+      </c>
+      <c r="C9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9" t="s">
         <v>411</v>
       </c>
-      <c r="C9" t="s">
-        <v>125</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>412</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>413</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
+        <v>232</v>
+      </c>
+      <c r="H9" t="s">
+        <v>349</v>
+      </c>
+      <c r="I9" t="s">
+        <v>229</v>
+      </c>
+      <c r="J9" t="s">
+        <v>132</v>
+      </c>
+      <c r="K9" t="s">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s">
         <v>414</v>
-      </c>
-      <c r="G9" t="s">
-        <v>233</v>
-      </c>
-      <c r="H9" t="s">
-        <v>350</v>
-      </c>
-      <c r="I9" t="s">
-        <v>230</v>
-      </c>
-      <c r="J9" t="s">
-        <v>133</v>
-      </c>
-      <c r="K9" t="s">
-        <v>133</v>
-      </c>
-      <c r="L9" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
+        <v>415</v>
+      </c>
+      <c r="C10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" t="s">
         <v>416</v>
       </c>
-      <c r="C10" t="s">
-        <v>125</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>417</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>418</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H10" t="s">
+        <v>349</v>
+      </c>
+      <c r="I10" t="s">
+        <v>229</v>
+      </c>
+      <c r="J10" t="s">
+        <v>132</v>
+      </c>
+      <c r="K10" t="s">
+        <v>132</v>
+      </c>
+      <c r="L10" t="s">
         <v>419</v>
-      </c>
-      <c r="G10" t="s">
-        <v>233</v>
-      </c>
-      <c r="H10" t="s">
-        <v>350</v>
-      </c>
-      <c r="I10" t="s">
-        <v>230</v>
-      </c>
-      <c r="J10" t="s">
-        <v>133</v>
-      </c>
-      <c r="K10" t="s">
-        <v>133</v>
-      </c>
-      <c r="L10" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D11" t="s">
+        <v>420</v>
+      </c>
+      <c r="E11" t="s">
         <v>421</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>422</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
+        <v>232</v>
+      </c>
+      <c r="H11" t="s">
+        <v>349</v>
+      </c>
+      <c r="I11" t="s">
+        <v>229</v>
+      </c>
+      <c r="J11" t="s">
+        <v>132</v>
+      </c>
+      <c r="K11" t="s">
+        <v>132</v>
+      </c>
+      <c r="L11" t="s">
         <v>423</v>
-      </c>
-      <c r="G11" t="s">
-        <v>233</v>
-      </c>
-      <c r="H11" t="s">
-        <v>350</v>
-      </c>
-      <c r="I11" t="s">
-        <v>230</v>
-      </c>
-      <c r="J11" t="s">
-        <v>133</v>
-      </c>
-      <c r="K11" t="s">
-        <v>133</v>
-      </c>
-      <c r="L11" t="s">
-        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -3854,146 +3838,146 @@
     <row r="1" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="D2" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="E2" s="16" t="s">
         <v>129</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>130</v>
       </c>
       <c r="F2" s="16"/>
       <c r="G2" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>134</v>
-      </c>
       <c r="E3" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
     </row>
     <row r="4" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C4" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="E4" s="15" t="s">
         <v>134</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>135</v>
       </c>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
     </row>
     <row r="5" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>137</v>
-      </c>
       <c r="E5" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F5" s="15"/>
       <c r="G5" s="15"/>
     </row>
     <row r="6" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="D6" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="E6" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="E6" s="15" t="s">
-        <v>141</v>
-      </c>
       <c r="F6" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G6" s="15"/>
     </row>
     <row r="7" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="C7" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="D7" s="15" t="s">
+      <c r="E7" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="E7" s="15" t="s">
-        <v>144</v>
-      </c>
       <c r="F7" s="15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="D8" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="E8" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="E8" s="15" t="s">
-        <v>148</v>
-      </c>
       <c r="F8" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G8" s="15"/>
     </row>
     <row r="9" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="D9" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>150</v>
-      </c>
       <c r="E9" s="17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G9" s="17"/>
     </row>
     <row r="10" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="17"/>
       <c r="C10" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
@@ -4003,7 +3987,7 @@
     <row r="11" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="17"/>
       <c r="C11" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D11" s="17"/>
       <c r="E11" s="17"/>
@@ -4012,26 +3996,26 @@
     </row>
     <row r="12" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="D12" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>152</v>
-      </c>
       <c r="E12" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G12" s="17"/>
     </row>
     <row r="13" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B13" s="17"/>
       <c r="C13" s="15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
@@ -4041,7 +4025,7 @@
     <row r="14" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B14" s="17"/>
       <c r="C14" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
@@ -4050,190 +4034,190 @@
     </row>
     <row r="15" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B15" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="D15" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>155</v>
-      </c>
       <c r="E15" s="15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="D16" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>158</v>
-      </c>
       <c r="E16" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="D17" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="C17" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>160</v>
-      </c>
       <c r="E17" s="15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="C18" s="15" t="s">
-        <v>162</v>
-      </c>
       <c r="D18" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G18" s="15"/>
     </row>
     <row r="19" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G19" s="15"/>
     </row>
     <row r="20" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G20" s="15"/>
     </row>
     <row r="21" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G21" s="15"/>
     </row>
     <row r="22" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B22" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G22" s="15"/>
     </row>
     <row r="23" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B23" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G23" s="15"/>
     </row>
     <row r="24" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B24" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="G24" s="17" t="s">
         <v>168</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
@@ -4241,31 +4225,31 @@
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
       <c r="E25" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G25" s="17"/>
     </row>
     <row r="26" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B26" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="D26" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="E26" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="D26" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>215</v>
-      </c>
       <c r="F26" s="15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.45">
@@ -4273,10 +4257,10 @@
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
       <c r="E27" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G27" s="17"/>
     </row>
@@ -4329,15 +4313,15 @@
     <row r="2" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B3" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C3" s="10">
         <v>32</v>
@@ -4349,7 +4333,7 @@
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B4" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C4" s="10">
         <f>C3*2</f>
@@ -4365,98 +4349,98 @@
     <row r="6" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="G6" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="L6" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="M6" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="N6" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="O6" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="O6" s="3" t="s">
+      <c r="P6" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B7" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="M7" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="N7" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B8" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" s="3">
         <v>16</v>
@@ -4503,11 +4487,11 @@
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B9" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -4520,15 +4504,15 @@
       <c r="M9" s="11"/>
       <c r="N9" s="11"/>
       <c r="O9" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B10" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -4547,11 +4531,11 @@
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B11" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
@@ -4568,11 +4552,11 @@
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B12" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -4589,7 +4573,7 @@
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B13" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -4604,13 +4588,13 @@
       <c r="M13" s="11"/>
       <c r="N13" s="11"/>
       <c r="O13" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P13" s="11"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B14" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C14" s="9">
         <f t="shared" ref="C14:P14" si="0">IF(C7="APB2",$D$4, $D$3)</f>
@@ -4671,7 +4655,7 @@
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B15" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C15" s="8">
         <v>0</v>
@@ -4718,7 +4702,7 @@
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B16" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C16" s="8">
         <v>0</v>
@@ -4765,7 +4749,7 @@
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B17" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C17" s="8">
         <f>C14/((C15+1)*(C16+1))</f>
@@ -4826,7 +4810,7 @@
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C18" s="8">
         <f>C17*1000</f>
@@ -4887,7 +4871,7 @@
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C19" s="8">
         <f>C18*1000</f>
@@ -4958,7 +4942,7 @@
   <sheetPr>
     <tabColor rgb="FF33CC33"/>
   </sheetPr>
-  <dimension ref="B2:K17"/>
+  <dimension ref="B2:J17"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" customWidth="1"/>
@@ -4968,12 +4952,11 @@
     <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="11.58203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
         <v>59</v>
       </c>
@@ -4996,18 +4979,15 @@
         <v>66</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.45">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B3" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>427</v>
@@ -5019,97 +4999,68 @@
         <v>63</v>
       </c>
       <c r="F3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G3" s="24">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="H3" s="24">
         <v>46281</v>
       </c>
       <c r="I3" t="s">
+        <v>429</v>
+      </c>
+      <c r="J3" t="s">
         <v>426</v>
       </c>
-      <c r="J3" t="s">
-        <v>430</v>
-      </c>
-      <c r="K3" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B4" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="D4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" t="s">
-        <v>433</v>
-      </c>
-      <c r="G4" s="24">
-        <v>46287</v>
-      </c>
-      <c r="H4" s="24">
-        <v>46288</v>
-      </c>
-      <c r="I4" t="s">
-        <v>434</v>
-      </c>
-      <c r="J4" t="s">
-        <v>430</v>
-      </c>
-      <c r="K4" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
